--- a/configs/onelake_security.xlsx
+++ b/configs/onelake_security.xlsx
@@ -629,7 +629,7 @@
       </x:c>
       <x:c r="T3" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Folder scope + RLS. Every NOT IN needs OR &lt;col&gt; IS NULL.</x:t>
+          <x:t xml:space="preserve">Folder scope + RLS. NOT IN drops NULL rows (three-valued logic) — either add OR &lt;col&gt; IS NULL, or satisfy yourself the column is never NULL. Over-rejects; never widens access.</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -860,7 +860,7 @@
         </x:is>
       </x:c>
       <x:c r="D2" s="7" t="str">
-        <x:v>OLAF v1.0.0 compatibility subset: alphanumeric, letter-first, &lt;= 124 chars. Re-check current SQL endpoint guidance: https://learn.microsoft.com/en-us/fabric/onelake/security/troubleshoot-onelake-security-for-sql-analytics-endpoints</x:v>
+        <x:v>OLAF compatibility subset: alphanumeric, letter-first, &lt;= 124 chars. Re-check current SQL endpoint guidance: https://learn.microsoft.com/en-us/fabric/onelake/security/troubleshoot-onelake-security-for-sql-analytics-endpoints</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
@@ -1282,7 +1282,7 @@
         <x:v>yes</x:v>
       </x:c>
       <x:c r="D22" s="7" t="str">
-        <x:v>OLAF v1.0.0 community Preview; evaluation only. The bulk DAR endpoint is Preview, not production-ready: https://learn.microsoft.com/en-us/rest/api/fabric/core/onelake-data-access-security/create-or-update-data-access-roles</x:v>
+        <x:v>OLAF community Preview; evaluation only. The bulk DAR endpoint is Preview, not production-ready: https://learn.microsoft.com/en-us/rest/api/fabric/core/onelake-data-access-security/create-or-update-data-access-roles</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="72" hidden="0" customHeight="1">
@@ -1439,7 +1439,7 @@
         <x:v>yes</x:v>
       </x:c>
       <x:c r="D5" s="7" t="str">
-        <x:v>OLAF v1.0.0 community Preview; synthetic template only. Re-check official sources before use.</x:v>
+        <x:v>OLAF community Preview; synthetic template only. Re-check official sources before use.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="72" hidden="0" customHeight="1">

--- a/configs/onelake_security.xlsx
+++ b/configs/onelake_security.xlsx
@@ -629,7 +629,7 @@
       </x:c>
       <x:c r="T3" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Folder scope + RLS. NOT IN drops NULL rows (three-valued logic) — either add OR &lt;col&gt; IS NULL, or satisfy yourself the column is never NULL. Over-rejects; never widens access.</x:t>
+          <x:t xml:space="preserve">Folder scope + RLS. NOT IN drops NULL rows — add OR &lt;col&gt; IS NULL or assert non-null.</x:t>
         </x:is>
       </x:c>
     </x:row>

--- a/configs/onelake_security.xlsx
+++ b/configs/onelake_security.xlsx
@@ -629,7 +629,7 @@
       </x:c>
       <x:c r="T3" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Folder scope + RLS. Every NOT IN needs OR &lt;col&gt; IS NULL.</x:t>
+          <x:t xml:space="preserve">Folder scope + RLS. NOT IN drops NULL rows — add OR &lt;col&gt; IS NULL or assert non-null.</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -860,7 +860,7 @@
         </x:is>
       </x:c>
       <x:c r="D2" s="7" t="str">
-        <x:v>OLAF v1.0.0 compatibility subset: alphanumeric, letter-first, &lt;= 124 chars. Re-check current SQL endpoint guidance: https://learn.microsoft.com/en-us/fabric/onelake/security/troubleshoot-onelake-security-for-sql-analytics-endpoints</x:v>
+        <x:v>OLAF compatibility subset: alphanumeric, letter-first, &lt;= 124 chars. Re-check current SQL endpoint guidance: https://learn.microsoft.com/en-us/fabric/onelake/security/troubleshoot-onelake-security-for-sql-analytics-endpoints</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
@@ -1282,7 +1282,7 @@
         <x:v>yes</x:v>
       </x:c>
       <x:c r="D22" s="7" t="str">
-        <x:v>OLAF v1.0.0 community Preview; evaluation only. The bulk DAR endpoint is Preview, not production-ready: https://learn.microsoft.com/en-us/rest/api/fabric/core/onelake-data-access-security/create-or-update-data-access-roles</x:v>
+        <x:v>OLAF community Preview; evaluation only. The bulk DAR endpoint is Preview, not production-ready: https://learn.microsoft.com/en-us/rest/api/fabric/core/onelake-data-access-security/create-or-update-data-access-roles</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="72" hidden="0" customHeight="1">
@@ -1439,7 +1439,7 @@
         <x:v>yes</x:v>
       </x:c>
       <x:c r="D5" s="7" t="str">
-        <x:v>OLAF v1.0.0 community Preview; synthetic template only. Re-check official sources before use.</x:v>
+        <x:v>OLAF community Preview; synthetic template only. Re-check official sources before use.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="72" hidden="0" customHeight="1">
